--- a/Bauteile/Bauteiliste.xlsx
+++ b/Bauteile/Bauteiliste.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Reaction-game\Bauteile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24229FC2-9E2C-4522-95BC-BE87815230AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF044EB-419F-4583-8E7F-A6C3C456CE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="40">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -50,18 +50,9 @@
     <t>Link</t>
   </si>
   <si>
-    <t>https://de.aliexpress.com/item/1005004648191254.html?spm=a2g0o.productlist.main.11.2459EPqMEPqMPa&amp;algo_pvid=71a2b90d-e209-469a-98aa-2a76762f0270&amp;algo_exp_id=71a2b90d-e209-469a-98aa-2a76762f0270-10&amp;pdp_ext_f=%7B%22order%22%3A%224%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%217.52%217.52%21%21%219.44%219.44%21%40211b61ae17780992084647705e8eee%2112000029972327325%21sea%21CH%211651786397%21X%211%210%21n_tag%3A-29919%3Bd%3A39b0672f%3Bm03_new_user%3A-29895&amp;curPageLogUid=kG1e6vMVdcb6&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005004648191254%7C_p_origin_prod%3A#nav-specification</t>
-  </si>
-  <si>
-    <t>https://de.aliexpress.com/item/1005008806055319.html?spm=a2g0o.productlist.main.4.1d4f22190w7VWl&amp;aem_p4p_detail=202605061352415960786670272220004805883&amp;algo_pvid=2daa20f7-a639-43f3-978f-2809a0db9ef7&amp;algo_exp_id=2daa20f7-a639-43f3-978f-2809a0db9ef7-3&amp;pdp_ext_f=%7B%22order%22%3A%22687%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%212.34%210.79%21%21%2120.03%216.76%21%402103985c17781007613643019e5d3b%2112000048167743767%21sea%21CH%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Ac3209689%3Bm03_new_user%3A-29895%3BpisId%3A5000000205009259&amp;curPageLogUid=gyNHzpHgPRcM&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008806055319%7C_p_origin_prod%3A&amp;search_p4p_id=202605061352415960786670272220004805883_1</t>
-  </si>
-  <si>
     <t>https://de.aliexpress.com/item/1005010609313908.html?spm=a2g0o.productlist.main.8.4ed7vmkhvmkhnx&amp;algo_pvid=f6c7520e-06f4-4ed3-8d0c-b6476542901d&amp;aem_p4p_detail=202605061355162449933969724320004384621&amp;algo_exp_id=f6c7520e-06f4-4ed3-8d0c-b6476542901d-7&amp;pdp_ext_f=%7B%22order%22%3A%226%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%217.58%216.79%21%21%219.52%218.53%21%402103868817781009163702091e2e8b%2112000052962992203%21sea%21CH%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Ac3209689%3Bm03_new_user%3A-29895&amp;curPageLogUid=9SGxunu0ocLL&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005010609313908%7C_p_origin_prod%3A&amp;search_p4p_id=202605061355162449933969724320004384621_2</t>
   </si>
   <si>
-    <t>https://de.aliexpress.com/item/1005008793748030.html?spm=a2g0o.productlist.main.16.5aa1IOIBIOIBwG&amp;aem_p4p_detail=2026050613593910402819930820000003847208&amp;algo_pvid=5a678aaf-dba1-424a-8509-6d5b66feac72&amp;algo_exp_id=5a678aaf-dba1-424a-8509-6d5b66feac72-15&amp;pdp_ext_f=%7B%22order%22%3A%22235%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%212.53%210.79%21%21%2121.70%216.80%21%40211b617b17781011796826279e4dac%2112000046686350619%21sea%21CH%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Ac3209689%3Bm03_new_user%3A-29895%3BpisId%3A5000000205238504&amp;curPageLogUid=e7RAkUPsRznq&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008793748030%7C_p_origin_prod%3A&amp;search_p4p_id=2026050613593910402819930820000003847208_4</t>
-  </si>
-  <si>
     <t>https://de.aliexpress.com/item/1005003521753549.html?spm=a2g0o.productlist.main.7.7402lLdilLdiCh&amp;algo_pvid=ec50bd99-0275-477c-9ae6-15df6132071c&amp;algo_exp_id=ec50bd99-0275-477c-9ae6-15df6132071c-6&amp;pdp_ext_f=%7B%22order%22%3A%22115%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%2119.39%2119.39%21%21%2124.34%2124.34%21%40211b819117781013078766625e1d85%2112000026350438711%21sea%21CH%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3Ac3209689%3Bm03_new_user%3A-29895&amp;curPageLogUid=NCuZZwQUqKnr&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005003521753549%7C_p_origin_prod%3A</t>
   </si>
   <si>
@@ -74,15 +65,9 @@
     <t>https://www.bastelgarage.ch/7-segment-xl-anzeige-6-5inch-sparkfun</t>
   </si>
   <si>
-    <t>https://www.wachendorff-prozesstechnik.de/produktgruppen/grossanzeigen/produkte/ld-serie-bis-25-m-50-m-ablesbar/Digitalanzeige-Einbaumessgeraet-Grossanzeige-6-stellig-LCD-Anzeige-LDT/</t>
-  </si>
-  <si>
     <t>https://www.schurter.com/de/datasheet/CPS</t>
   </si>
   <si>
-    <t>3-101-429</t>
-  </si>
-  <si>
     <t>Hersteller</t>
   </si>
   <si>
@@ -92,9 +77,6 @@
     <t>Mouser</t>
   </si>
   <si>
-    <t>Taster Kapazitiv multicolor Ringbeleuchtung</t>
-  </si>
-  <si>
     <t>Taster Kapazitiv multicolor Flächenbeleuchtung</t>
   </si>
   <si>
@@ -107,9 +89,6 @@
     <t>693-3-101-424</t>
   </si>
   <si>
-    <t>693-3-101-429</t>
-  </si>
-  <si>
     <t>Relaisboard 8 Relais 5V</t>
   </si>
   <si>
@@ -128,13 +107,64 @@
     <t>Aliexpress</t>
   </si>
   <si>
-    <t>S</t>
+    <t>https://de.aliexpress.com/item/32652265981.html?spm=a2g0o.productlist.main.13.4866mOkBmOkBJR&amp;utparam-url=scene%3Asearch%7Cquery_from%3Apc_back_same_best%7Cx_object_id%3A32652265981%7C_p_origin_prod%3A&amp;algo_pvid=88cc101c-8597-4f92-b5e3-cf739fa45ad3&amp;algo_exp_id=88cc101c-8597-4f92-b5e3-cf739fa45ad3&amp;pdp_ext_f=%7B%22order%22%3A%22186%22%2C%22spu_best_type%22%3A%22price%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%211.33%211.27%21%21%211.66%211.58%21%402103909217789393980926887e21a9%2159735521975%21sea%21CH%214202101768%21ACX%211%210%21n_tag%3A-29919%3Bd%3Ac3209689%3Bm03_new_user%3A-29894</t>
+  </si>
+  <si>
+    <t>Treibermodule für LED's</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/1005011956506357.html?spm=a2g0o.productlist.main.2.3538RnAnRnAnDD&amp;algo_pvid=72ed8ef0-c6a8-408e-9603-02303aaabc8a&amp;algo_exp_id=72ed8ef0-c6a8-408e-9603-02303aaabc8a-1&amp;pdp_ext_f=%7B%22order%22%3A%2264%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%214.19%210.79%21%21%2135.59%216.72%21%402103890117789396146217685e08c7%2112000057130536335%21sea%21CH%214202101768%21ACX%211%210%21n_tag%3A-29919%3Bd%3Ac3209689%3Bm03_new_user%3A-29894%3BpisId%3A5000000203266523&amp;curPageLogUid=3d4u2AC8t2MR&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005011956506357%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>Relaisboard 8 Relais 24V</t>
+  </si>
+  <si>
+    <t>Logiclevelshifter 8 Kanal 3.3V-5V</t>
+  </si>
+  <si>
+    <t>Bastelgarage</t>
+  </si>
+  <si>
+    <t>LED 7-Segment-Anzeige 150mm hoch</t>
+  </si>
+  <si>
+    <t>Sparkfun</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/1005011636640617.html?spm=a2g0o.productlist.main.1.6173XeW1XeW19z&amp;algo_pvid=b38d4873-eaf9-4b7a-a4f4-df6e029b773c&amp;algo_exp_id=b38d4873-eaf9-4b7a-a4f4-df6e029b773c-0&amp;pdp_ext_f=%7B%22order%22%3A%223%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%212.24%212.24%21%21%2119.03%2119.03%21%402103864c17789441357548105eee98%2112000056122702360%21sea%21CH%214202101768%21ACX%211%210%21n_tag%3A-29919%3Bd%3Ac3209689%3Bm03_new_user%3A-29894&amp;curPageLogUid=MVbVJggmKhSQ&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005011636640617%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>Logiclevelshifter IC</t>
+  </si>
+  <si>
+    <t>32 GPIO extender via I2C für DIN Schiene</t>
+  </si>
+  <si>
+    <t>Breakoutboard für ESP32 für DIN Schiene</t>
+  </si>
+  <si>
+    <t>https://de.aliexpress.com/item/1005008503831020.html?spm=a2g0o.productlist.main.1.3af4p7SKp7SKFT&amp;algo_pvid=4e3a5c21-2325-4e4a-94b8-b488434e7ceb&amp;algo_exp_id=4e3a5c21-2325-4e4a-94b8-b488434e7ceb-0&amp;pdp_ext_f=%7B%22order%22%3A%222937%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CHF%214.23%210.79%21%21%2135.92%216.72%21%40211b6c1717789448226875910e25f4%2112000045457574256%21sea%21CH%214202101768%21ACX%211%210%21n_tag%3A-29919%3Bd%3Ac3209689%3Bm03_new_user%3A-29894%3BpisId%3A5000000203266461&amp;curPageLogUid=q7lFXxjVziFX&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008503831020%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>ESP32</t>
+  </si>
+  <si>
+    <t>Netzteil 24V 20W</t>
+  </si>
+  <si>
+    <t>Netzteil 12V 20W</t>
+  </si>
+  <si>
+    <t>Netzteil 5V 20W</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="_ [$CHF-807]\ * #,##0.00_ ;_ [$CHF-807]\ * \-#,##0.00_ ;_ [$CHF-807]\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -144,9 +174,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color theme="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -169,16 +199,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -457,212 +494,439 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="38.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.796875" customWidth="1"/>
-    <col min="3" max="3" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" customWidth="1"/>
+    <col min="2" max="2" width="8.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="16.3984375" customWidth="1"/>
+    <col min="6" max="6" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3">
+        <v>48</v>
+      </c>
+      <c r="H2" s="3">
+        <f>F2*G2</f>
+        <v>720</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>6.62</v>
+      </c>
+      <c r="H3" s="3">
+        <f>F3*G3</f>
+        <v>13.24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="H4" s="3">
+        <f t="shared" ref="H4:H14" si="0">F4*G4</f>
+        <v>6.35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="H5" s="3">
+        <f t="shared" si="0"/>
+        <v>3.95</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>8.35</v>
+      </c>
+      <c r="H6" s="3">
+        <f t="shared" si="0"/>
+        <v>16.7</v>
+      </c>
+      <c r="I6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2">
+        <v>420332</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3">
+        <v>34.9</v>
+      </c>
+      <c r="H7" s="3">
+        <f>G7*F7</f>
+        <v>139.6</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G8" s="3">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="H8" s="3">
+        <f>G8*F8</f>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>20</v>
+      </c>
+      <c r="H9" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="I9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
+        <v>5.22</v>
+      </c>
+      <c r="H10" s="3">
+        <f t="shared" si="0"/>
+        <v>5.22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="1">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I9" t="s">
+      <c r="G11" s="3">
+        <v>0.79</v>
+      </c>
+      <c r="H11" s="3">
+        <f t="shared" si="0"/>
+        <v>1.58</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>5.31</v>
+      </c>
+      <c r="H12" s="3">
+        <f t="shared" si="0"/>
+        <v>5.31</v>
+      </c>
+      <c r="I12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I12" t="s">
-        <v>10</v>
-      </c>
-    </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>5.59</v>
+      </c>
+      <c r="H13" s="3">
+        <f t="shared" si="0"/>
+        <v>5.59</v>
+      </c>
       <c r="I13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I14" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I15" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16">
-        <v>15</v>
-      </c>
-      <c r="G16">
-        <v>42</v>
-      </c>
-      <c r="H16">
-        <f>F16*G16</f>
-        <v>630</v>
-      </c>
-      <c r="I16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17">
-        <v>15</v>
-      </c>
-      <c r="G17">
-        <v>48</v>
-      </c>
-      <c r="H17">
-        <f>F17*G17</f>
-        <v>720</v>
-      </c>
-      <c r="I17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <v>6.62</v>
-      </c>
-      <c r="H18">
-        <f>F18*G18</f>
-        <v>13.24</v>
-      </c>
-      <c r="I18" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>30</v>
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>5.27</v>
+      </c>
+      <c r="H14" s="3">
+        <f t="shared" si="0"/>
+        <v>5.27</v>
+      </c>
+      <c r="I14" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="I14" r:id="rId1" xr:uid="{A31E83B1-8E36-4C12-91E0-5653F8F02C26}"/>
-    <hyperlink ref="I15" r:id="rId2" xr:uid="{4D94FB27-E285-454B-B3A8-909F68090BE7}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Bauteile/Bauteiliste.xlsx
+++ b/Bauteile/Bauteiliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Reaction-game\Bauteile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF044EB-419F-4583-8E7F-A6C3C456CE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316980DE-3310-4258-9790-D7CC1AB02517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="52">
   <si>
     <t>Bezeichnung</t>
   </si>
@@ -89,9 +89,6 @@
     <t>693-3-101-424</t>
   </si>
   <si>
-    <t>Relaisboard 8 Relais 5V</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -156,6 +153,45 @@
   </si>
   <si>
     <t>Netzteil 5V 20W</t>
+  </si>
+  <si>
+    <t>Schlüsselschalter inkl. 2 Schlüssel</t>
+  </si>
+  <si>
+    <t>Lorlin</t>
+  </si>
+  <si>
+    <t>SRL-5-L-S-2</t>
+  </si>
+  <si>
+    <t>135-04-487</t>
+  </si>
+  <si>
+    <t>Distrelec</t>
+  </si>
+  <si>
+    <t>KEY901 SPARE</t>
+  </si>
+  <si>
+    <t>135-04-425</t>
+  </si>
+  <si>
+    <t>Schlüssel zu Schlüsselschalter (2 Stück pro Einheit)</t>
+  </si>
+  <si>
+    <t>https://www.distrelec.ch/de/ersatzschluessel-gleichen-nickel-srl-series-switch-lorlin-key901-spare/p/13504425?itemList=compatible</t>
+  </si>
+  <si>
+    <t>https://www.distrelec.ch/de/schluesselschalter-wechsler-24-vdc-115-vac-pos-60-lorlin-srl/p/13504487</t>
+  </si>
+  <si>
+    <t>Bestellt</t>
+  </si>
+  <si>
+    <t>Lieferdatum</t>
+  </si>
+  <si>
+    <t>Angekommen</t>
   </si>
 </sst>
 </file>
@@ -163,7 +199,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="_ [$CHF-807]\ * #,##0.00_ ;_ [$CHF-807]\ * \-#,##0.00_ ;_ [$CHF-807]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ [$CHF-807]\ * #,##0.00_ ;_ [$CHF-807]\ * \-#,##0.00_ ;_ [$CHF-807]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -202,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -210,10 +246,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -494,10 +533,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="38.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
@@ -505,9 +544,12 @@
     <col min="6" max="6" width="8.06640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -524,19 +566,28 @@
         <v>15</v>
       </c>
       <c r="F1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="I1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -556,374 +607,502 @@
         <v>15</v>
       </c>
       <c r="G2" s="3">
-        <v>48</v>
+        <v>43.56</v>
       </c>
       <c r="H2" s="3">
         <f>F2*G2</f>
-        <v>720</v>
-      </c>
-      <c r="I2" t="s">
+        <v>653.40000000000009</v>
+      </c>
+      <c r="I2" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J2" s="5">
+        <v>46164</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="L2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1">
+        <v>5</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.27</v>
+      </c>
+      <c r="H3" s="3">
+        <f t="shared" ref="H3:H15" si="0">F3*G3</f>
+        <v>6.35</v>
+      </c>
+      <c r="I3" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J3" s="5">
+        <v>46177</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="1">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>6.62</v>
-      </c>
-      <c r="H3" s="3">
-        <f>F3*G3</f>
-        <v>13.24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1">
         <v>5</v>
       </c>
       <c r="G4" s="3">
-        <v>1.27</v>
+        <v>0.79</v>
       </c>
       <c r="H4" s="3">
-        <f t="shared" ref="H4:H14" si="0">F4*G4</f>
-        <v>6.35</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+        <f t="shared" si="0"/>
+        <v>3.95</v>
+      </c>
+      <c r="I4" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J4" s="5">
+        <v>46175</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="3">
-        <v>0.79</v>
+        <v>8.35</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" si="0"/>
-        <v>3.95</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+        <v>16.7</v>
+      </c>
+      <c r="I5" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J5" s="5">
+        <v>46175</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="E6" s="2">
+        <v>420332</v>
       </c>
       <c r="F6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="3">
-        <v>8.35</v>
+        <v>34.9</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="0"/>
-        <v>16.7</v>
-      </c>
-      <c r="I6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+        <f>G6*F6</f>
+        <v>139.6</v>
+      </c>
+      <c r="I6" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J6" s="5">
+        <v>46164</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="2">
-        <v>420332</v>
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="F7" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3">
-        <v>34.9</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="H7" s="3">
         <f>G7*F7</f>
-        <v>139.6</v>
-      </c>
-      <c r="I7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I7" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J7" s="5">
+        <v>46175</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="3">
-        <v>2.2400000000000002</v>
+        <v>19.489999999999998</v>
       </c>
       <c r="H8" s="3">
-        <f>G8*F8</f>
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+        <f t="shared" si="0"/>
+        <v>19.489999999999998</v>
+      </c>
+      <c r="I8" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J8" s="5">
+        <v>46177</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>20</v>
+        <v>5.22</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="I9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+        <v>5.22</v>
+      </c>
+      <c r="I9" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J9" s="5">
+        <v>46175</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="3">
-        <v>5.22</v>
+        <v>7.7</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" si="0"/>
-        <v>5.22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+        <v>15.4</v>
+      </c>
+      <c r="I10" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J10" s="5">
+        <v>46175</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3">
-        <v>0.79</v>
+        <v>8.89</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" si="0"/>
-        <v>1.58</v>
-      </c>
-      <c r="I11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+        <v>8.89</v>
+      </c>
+      <c r="I11" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J11" s="5">
+        <v>46175</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
       </c>
       <c r="G12" s="3">
-        <v>5.31</v>
+        <v>8.99</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" si="0"/>
-        <v>5.31</v>
-      </c>
-      <c r="I12" t="s">
+        <v>8.99</v>
+      </c>
+      <c r="I12" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J12" s="5">
+        <v>46175</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1">
         <v>1</v>
       </c>
       <c r="G13" s="3">
-        <v>5.59</v>
+        <v>8.91</v>
       </c>
       <c r="H13" s="3">
         <f t="shared" si="0"/>
-        <v>5.59</v>
-      </c>
-      <c r="I13" t="s">
+        <v>8.91</v>
+      </c>
+      <c r="I13" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J13" s="5">
+        <v>46175</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
       </c>
       <c r="G14" s="3">
-        <v>5.27</v>
+        <v>6.1</v>
       </c>
       <c r="H14" s="3">
         <f t="shared" si="0"/>
-        <v>5.27</v>
-      </c>
-      <c r="I14" t="s">
-        <v>7</v>
+        <v>6.1</v>
+      </c>
+      <c r="I14" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J14" s="5">
+        <v>46161</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="H15" s="3">
+        <f t="shared" si="0"/>
+        <v>24.4</v>
+      </c>
+      <c r="I15" s="5">
+        <v>46159</v>
+      </c>
+      <c r="J15" s="5">
+        <v>46161</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/Bauteile/Bauteiliste.xlsx
+++ b/Bauteile/Bauteiliste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Reaction-game\Bauteile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\private\reaction-game\Bauteile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF044EB-419F-4583-8E7F-A6C3C456CE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E1C909-0315-4CCD-933B-2C8A4C8837CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1886" yWindow="1886" windowWidth="18514" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -163,9 +163,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="_ [$CHF-807]\ * #,##0.00_ ;_ [$CHF-807]\ * \-#,##0.00_ ;_ [$CHF-807]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ [$CHF-807]\ * #,##0.00_ ;_ [$CHF-807]\ * \-#,##0.00_ ;_ [$CHF-807]\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +177,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -199,10 +207,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -210,12 +219,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -495,19 +506,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="38.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.69140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.69140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="255.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -536,7 +548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -562,11 +574,11 @@
         <f>F2*G2</f>
         <v>720</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -596,7 +608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -626,7 +638,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -656,7 +668,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -686,7 +698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -712,11 +724,11 @@
         <f>G7*F7</f>
         <v>139.6</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -746,7 +758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -776,7 +788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -806,7 +818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -836,7 +848,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -866,7 +878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -896,7 +908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -927,6 +939,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I7" r:id="rId1" xr:uid="{9CC24E8E-4E7D-4B41-B345-452B6CD87019}"/>
+    <hyperlink ref="I2" r:id="rId2" xr:uid="{F4578119-DE35-4867-ABD4-528CB7B0D3D3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Bauteile/Bauteiliste.xlsx
+++ b/Bauteile/Bauteiliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\private\reaction-game\Bauteile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E1C909-0315-4CCD-933B-2C8A4C8837CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F06D5DC-BB21-422B-AE97-D6267BC6F8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1886" yWindow="1886" windowWidth="18514" windowHeight="10740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
